--- a/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -780,15 +780,51 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="42" t="str"/>
-      <c r="B10" s="42" t="str"/>
-      <c r="C10" s="42" t="str"/>
-      <c r="D10" s="42" t="str"/>
-      <c r="E10" s="42" t="str"/>
-      <c r="F10" s="42" t="str"/>
-      <c r="G10" s="42" t="str"/>
-      <c r="H10" s="42" t="str"/>
-      <c r="I10" s="42" t="str"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OEM-SR-001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SWR-007</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CMP-002a CrashReleaseHandler</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,12 +834,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SWR-007</t>
+          <t>SWR-008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002a CrashReleaseHandler</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -833,24 +869,24 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1)</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OEM-SR-001</t>
+          <t>OEM-SR-002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SWR-008</t>
+          <t>SWR-005</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002c ApproachRiskHandler</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -880,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); PENDING=NONE 가정, OEM 재확인 필요</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -892,12 +928,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SWR-005</t>
+          <t>SWR-006</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002c ApproachRiskHandler</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -927,7 +963,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1)</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -939,12 +975,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SWR-006</t>
+          <t>SWR-009</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002c ApproachRiskHandler</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -974,24 +1010,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); override(FR-003)는 Phase2에서 확장</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OEM-SR-002</t>
+          <t>OEM-SR-003</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SWR-009</t>
+          <t>SWR-013a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-001 InputValidator</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1021,7 +1057,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); 인터페이스 계약(OEM-IF-003)에서 파생</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1069,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SWR-013a</t>
+          <t>SWR-013b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-001 InputValidator</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1068,24 +1104,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); 원자성 분리(013→013a/b)</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OEM-SR-003</t>
+          <t>OEM-SR-004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SWR-013b</t>
+          <t>SWR-021a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002b SensorFaultHandler</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1115,7 +1151,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); 원자성 분리(013→013a/b)</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1163,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SWR-021a</t>
+          <t>SWR-021b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CMP-002b SensorFaultHandler</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1162,99 +1198,52 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>요구사항만 작성(Phase1); 원자성 분리(021→021a/b)</t>
+          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OEM-SR-004</t>
+          <t>(확인필요)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SWR-021b</t>
+          <t>SWR-019</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>요구사항만 작성(Phase1); 원자성 분리(021→021a/b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>(확인필요)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SWR-019</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>OEM-SWR-001 9장 추적표에 매핑 없음 - 결번/누락 여부 OEM 재확인 필요</t>
         </is>
@@ -1287,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1461,6 +1450,38 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>architecture-designer(AI)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phase 1 아키텍처(계층형+책임연쇄) 할당 반영 — Architecture 열 갱신</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>사용자 검토 대기</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-003 CrashReleaseHandler.tryHandle</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-003 CrashReleaseHandler.tryHandle</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-005 ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-005 ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-005 ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-001 InputValidator.getValidatedSignal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-001 InputValidator.getValidatedSignal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-004 SensorFaultHandler.tryHandle</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>UNIT-004 SensorFaultHandler.tryHandle</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처 할당 완료(Phase1)</t>
+          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1482,6 +1482,38 @@
         </is>
       </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>detailed-designer(AI)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Phase 1 상세설계(7개 유닛) 할당 반영 — Detailed Design 열 갱신</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>사용자 검토 대기</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -802,12 +802,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/crash_release_handler.py::CrashReleaseHandler.tryHandle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_crash_release_handler.py</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/crash_release_handler.py::CrashReleaseHandler.tryHandle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_crash_release_handler.py</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/approach_risk_handler.py::ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_approach_risk_handler.py</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/approach_risk_handler.py::ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_approach_risk_handler.py</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/approach_risk_handler.py::ApproachRiskHandler.tryHandle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_approach_risk_handler.py</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/input_validator.py::InputValidator.getValidatedSignal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_input_validator.py</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/input_validator.py::InputValidator.getValidatedSignal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_input_validator.py</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/sensor_fault_handler.py::SensorFaultHandler.tryHandle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_sensor_fault_handler.py</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>src/childlock/handlers/sensor_fault_handler.py::SensorFaultHandler.tryHandle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>tests/unit/test_sensor_fault_handler.py</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>요구사항+아키텍처+상세설계 할당 완료(Phase1)</t>
+          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1514,6 +1514,38 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>coding(AI)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Phase 1 구현(7개 유닛, 32개 단위테스트) — Code/SWE.4 열 갱신, Branch 커버리지 100%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>사용자 검토 대기</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -812,17 +812,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>INT-CASE-001, INT-CASE-007</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>INT-CASE-001</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -906,17 +906,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>INT-CASE-002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -953,17 +953,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>INT-CASE-002</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>INT-CASE-002</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1047,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>INT-CASE-005</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>INT-CASE-006</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1141,17 +1141,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>INT-CASE-003, INT-CASE-008</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>INT-CASE-003, INT-CASE-008</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Branch 100%, 테스트 성공률 100%(32/32) — coding 단계 완료</t>
+          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1546,6 +1546,38 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>integration-tester(AI)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phase 1 통합시험(10 케이스) 완료 — SWE.5 열 갱신</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>사용자 검토 대기</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>

--- a/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
+++ b/traceability/TRC-001_양방향 요구사항 추적 매트릭스.xlsx
@@ -864,12 +864,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-002</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-003</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-004</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-005</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-006</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-007</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-008</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>VER-CASE-009</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>단위+통합 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외)</t>
+          <t>단위+통합+시스템 시험 완료(Phase1), Branch/함수/Call 커버리지 100%(pragma로 방어코드 3라인 제외), 요구사항 커버리지 100%, 전체 테스트 성공률 100%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1578,6 +1578,38 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>미승인</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sw-system-tester(AI)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Phase 1 시스템 테스트(9 케이스) 완료 — SWE.6 열 갱신, 요구사항 커버리지 100%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>사용자 검토 대기</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>미승인</t>
         </is>
